--- a/Project_SomethingAwesome/Project/outputs/requirements/Signal_Forge_CTF_Tasks.xlsx
+++ b/Project_SomethingAwesome/Project/outputs/requirements/Signal_Forge_CTF_Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GithubRepositories\COMP6841\Project_SomethingAwesome\Project\outputs\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04CA9CB1-F97E-4214-8297-FD36FD4E92E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869396F2-FCE2-479A-9FC5-9113E43B3940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="108">
   <si>
     <t>Context ID</t>
   </si>
@@ -419,16 +419,29 @@
   <si>
     <t>FLAG{HI_THERE_IM_DORY}</t>
   </si>
+  <si>
+    <t>FLAG{WHISKY TANGO FOXTROT I AM EXPOSED} AND FLAG{QUADRATURE AND CONFUSED}</t>
+  </si>
+  <si>
+    <t>FLAG{RANDU AINT GROGU}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -445,7 +458,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -478,6 +491,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,128 +600,158 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -830,6 +885,19 @@
       </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -906,19 +974,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table4" displayName="Table4" ref="A1:J32" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table4" displayName="Table4" ref="A1:J32" totalsRowShown="0" dataDxfId="10">
   <autoFilter ref="A1:J32" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="10">
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Context ID" dataDxfId="10"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task ID" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Context" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Sub Task" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Details" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="CTF Flag Location" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Level" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Evidence (Screenshot)" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Comments" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{E954B8EC-DB5F-4073-99C1-CA5B930FC830}" name="Flag" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Context ID" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Context" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Sub Task" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Details" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="CTF Flag Location" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Level" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Evidence (Screenshot)" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Comments" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{E954B8EC-DB5F-4073-99C1-CA5B930FC830}" name="Flag" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1166,727 +1234,731 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="23" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A2" s="42">
+    <row r="2" spans="1:10" s="9" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="28">
         <v>1</v>
       </c>
-      <c r="B2" s="42">
+      <c r="B2" s="28">
         <v>1</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40" t="s">
+      <c r="H2" s="26"/>
+      <c r="I2" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="26" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A3" s="37">
+    <row r="3" spans="1:10" s="10" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="23">
         <v>1</v>
       </c>
-      <c r="B3" s="37">
+      <c r="B3" s="23">
         <v>1.01</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="40" t="s">
+      <c r="F3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="41"/>
-      <c r="I3" s="40" t="s">
+      <c r="H3" s="27"/>
+      <c r="I3" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="40" t="s">
+      <c r="J3" s="26" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="37">
+    <row r="4" spans="1:10" s="10" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="23">
         <v>1</v>
       </c>
-      <c r="B4" s="37">
+      <c r="B4" s="23">
         <v>1.02</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="41"/>
-      <c r="I4" s="40" t="s">
+      <c r="H4" s="27"/>
+      <c r="I4" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="40" t="s">
+      <c r="J4" s="26" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="37">
+    <row r="5" spans="1:10" s="10" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="23">
         <v>1</v>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="23">
         <v>1.03</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="41"/>
-      <c r="I5" s="40" t="s">
+      <c r="H5" s="27"/>
+      <c r="I5" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="40" t="s">
+      <c r="J5" s="26" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="44" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A6" s="37">
+    <row r="6" spans="1:10" s="30" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="23">
         <v>2</v>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="23">
         <v>2</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="41"/>
-      <c r="I6" s="43" t="s">
+      <c r="H6" s="27"/>
+      <c r="I6" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="43" t="s">
+      <c r="J6" s="29" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="44" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" s="37">
+    <row r="7" spans="1:10" s="30" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="23">
         <v>2</v>
       </c>
-      <c r="B7" s="37">
+      <c r="B7" s="23">
         <v>2.0099999999999998</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="41"/>
-      <c r="I7" s="43" t="s">
+      <c r="H7" s="27"/>
+      <c r="I7" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="43" t="s">
+      <c r="J7" s="29" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="44" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="37">
+    <row r="8" spans="1:10" s="30" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="23">
         <v>2</v>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="23">
         <v>2.02</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="40" t="s">
+      <c r="F8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="41"/>
-      <c r="I8" s="43" t="s">
+      <c r="H8" s="27"/>
+      <c r="I8" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="43" t="s">
+      <c r="J8" s="29" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="44" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="37">
+    <row r="9" spans="1:10" s="30" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="23">
         <v>2</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="23">
         <v>2.0299999999999998</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="40" t="s">
+      <c r="E9" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="38" t="s">
+      <c r="G9" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="41"/>
-      <c r="I9" s="43" t="s">
+      <c r="H9" s="27"/>
+      <c r="I9" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="43" t="s">
+      <c r="J9" s="29" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="30" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="25">
+    <row r="10" spans="1:10" s="53" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="46">
         <v>3</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="46">
         <v>3</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G10" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="29"/>
-      <c r="I10" s="31" t="s">
+      <c r="H10" s="51"/>
+      <c r="I10" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="31"/>
-    </row>
-    <row r="11" spans="1:10" s="30" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="25">
+      <c r="J10" s="48" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="53" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="46">
         <v>3</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="46">
         <v>3.01</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="29"/>
-      <c r="I11" s="31" t="s">
+      <c r="H11" s="51"/>
+      <c r="I11" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="31"/>
-    </row>
-    <row r="12" spans="1:10" s="30" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="25">
+      <c r="J11" s="48" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="61" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="54">
         <v>3</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="54">
         <v>3.02</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G12" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="29"/>
-      <c r="I12" s="31" t="s">
+      <c r="H12" s="59"/>
+      <c r="I12" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="31"/>
-    </row>
-    <row r="13" spans="1:10" s="30" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="25">
+      <c r="J12" s="60"/>
+    </row>
+    <row r="13" spans="1:10" s="16" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="11">
         <v>4</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="29"/>
-      <c r="I13" s="31" t="s">
+      <c r="H13" s="15"/>
+      <c r="I13" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="31"/>
-    </row>
-    <row r="14" spans="1:10" s="30" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="25">
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10" s="16" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="11">
         <v>4</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="11">
         <v>4.01</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="27" t="s">
+      <c r="G14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="29"/>
-      <c r="I14" s="31" t="s">
+      <c r="H14" s="15"/>
+      <c r="I14" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J14" s="31"/>
-    </row>
-    <row r="15" spans="1:10" s="30" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="25">
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15" spans="1:10" s="16" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="11">
         <v>4</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="11">
         <v>4.0199999999999996</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="G15" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="29"/>
-      <c r="I15" s="31" t="s">
+      <c r="H15" s="15"/>
+      <c r="I15" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="J15" s="31"/>
-    </row>
-    <row r="16" spans="1:10" s="30" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="25">
+      <c r="J15" s="17"/>
+    </row>
+    <row r="16" spans="1:10" s="16" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="11">
         <v>5</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="11">
         <v>5.01</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="28" t="s">
+      <c r="F16" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="G16" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="29"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-    </row>
-    <row r="17" spans="1:10" s="30" customFormat="1" ht="31" x14ac:dyDescent="0.35">
-      <c r="A17" s="25">
+      <c r="H16" s="15"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" spans="1:10" s="16" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="11">
         <v>5</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="11">
         <v>5.0199999999999996</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="28" t="s">
+      <c r="F17" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="G17" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="29"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-    </row>
-    <row r="18" spans="1:10" s="30" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="25">
+      <c r="H17" s="15"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" spans="1:10" s="16" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="11">
         <v>5</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="11">
         <v>5.03</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="27" t="s">
+      <c r="G18" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="29"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-    </row>
-    <row r="19" spans="1:10" s="30" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="25">
+      <c r="H18" s="15"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:10" s="16" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="11">
         <v>5</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="11">
         <v>5.04</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-    </row>
-    <row r="20" spans="1:10" s="30" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="25">
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+    </row>
+    <row r="20" spans="1:10" s="16" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="11">
         <v>6</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="11">
         <v>6.01</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="28" t="s">
+      <c r="F20" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="G20" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="H20" s="29"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-    </row>
-    <row r="21" spans="1:10" s="30" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="25">
+      <c r="H20" s="15"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" s="16" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="11">
         <v>6</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="11">
         <v>6.02</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="F21" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G21" s="27" t="s">
+      <c r="G21" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="H21" s="29"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-    </row>
-    <row r="22" spans="1:10" s="30" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A22" s="25">
+      <c r="H21" s="15"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:10" s="16" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A22" s="11">
         <v>6</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="11">
         <v>6.03</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E22" s="31" t="s">
+      <c r="E22" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G22" s="27" t="s">
+      <c r="G22" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="H22" s="29"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-    </row>
-    <row r="23" spans="1:10" s="30" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A23" s="25">
+      <c r="H22" s="15"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="1:10" s="16" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A23" s="11">
         <v>6</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="11">
         <v>6.04</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="31" t="s">
+      <c r="E23" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G23" s="27" t="s">
+      <c r="G23" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="H23" s="29"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1919,1063 +1991,1145 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11" t="s">
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="13" t="s">
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14"/>
-      <c r="AG1" s="14"/>
-      <c r="AH1" s="14"/>
-      <c r="AI1" s="15"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="35"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
     <row r="2" spans="1:37" ht="256.64999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6" t="e" vm="1">
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="7" t="s">
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="39"/>
+      <c r="W2" s="39"/>
+      <c r="X2" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8"/>
-      <c r="AB2" s="8"/>
-      <c r="AC2" s="8"/>
-      <c r="AD2" s="8"/>
-      <c r="AE2" s="8"/>
-      <c r="AF2" s="8"/>
-      <c r="AG2" s="8"/>
-      <c r="AH2" s="8"/>
-      <c r="AI2" s="8"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="41"/>
+      <c r="AH2" s="41"/>
+      <c r="AI2" s="41"/>
     </row>
     <row r="3" spans="1:37" ht="135.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="2" t="e" vm="2">
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="38" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="9" t="s">
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
-      <c r="AB3" s="10"/>
-      <c r="AC3" s="10"/>
-      <c r="AD3" s="10"/>
-      <c r="AE3" s="10"/>
-      <c r="AF3" s="10"/>
-      <c r="AG3" s="10"/>
-      <c r="AH3" s="10"/>
-      <c r="AI3" s="10"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="32"/>
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="32"/>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="32"/>
+      <c r="AF3" s="32"/>
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
     </row>
     <row r="4" spans="1:37" ht="169.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="2" t="s">
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="e" vm="2">
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="9" t="s">
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39"/>
+      <c r="W4" s="39"/>
+      <c r="X4" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="10"/>
-      <c r="AF4" s="10"/>
-      <c r="AG4" s="10"/>
-      <c r="AH4" s="10"/>
-      <c r="AI4" s="10"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="32"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="32"/>
+      <c r="AE4" s="32"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="32"/>
+      <c r="AH4" s="32"/>
+      <c r="AI4" s="32"/>
     </row>
     <row r="5" spans="1:37" ht="193" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="2" t="s">
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6" t="e" vm="2">
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="9" t="s">
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="39"/>
+      <c r="S5" s="39"/>
+      <c r="T5" s="39"/>
+      <c r="U5" s="39"/>
+      <c r="V5" s="39"/>
+      <c r="W5" s="39"/>
+      <c r="X5" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10"/>
-      <c r="AB5" s="10"/>
-      <c r="AC5" s="10"/>
-      <c r="AD5" s="10"/>
-      <c r="AE5" s="10"/>
-      <c r="AF5" s="10"/>
-      <c r="AG5" s="10"/>
-      <c r="AH5" s="10"/>
-      <c r="AI5" s="10"/>
+      <c r="Y5" s="32"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="32"/>
+      <c r="AC5" s="32"/>
+      <c r="AD5" s="32"/>
+      <c r="AE5" s="32"/>
+      <c r="AF5" s="32"/>
+      <c r="AG5" s="32"/>
+      <c r="AH5" s="32"/>
+      <c r="AI5" s="32"/>
     </row>
     <row r="6" spans="1:37" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="2" t="s">
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6" t="e" vm="2">
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="9" t="s">
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="W6" s="39"/>
+      <c r="X6" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="10"/>
-      <c r="AA6" s="10"/>
-      <c r="AB6" s="10"/>
-      <c r="AC6" s="10"/>
-      <c r="AD6" s="10"/>
-      <c r="AE6" s="10"/>
-      <c r="AF6" s="10"/>
-      <c r="AG6" s="10"/>
-      <c r="AH6" s="10"/>
-      <c r="AI6" s="10"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="32"/>
+      <c r="AE6" s="32"/>
+      <c r="AF6" s="32"/>
+      <c r="AG6" s="32"/>
+      <c r="AH6" s="32"/>
+      <c r="AI6" s="32"/>
     </row>
     <row r="7" spans="1:37" ht="106" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="e" vm="2">
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="9" t="s">
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="38"/>
+      <c r="V7" s="38"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="10"/>
-      <c r="AA7" s="10"/>
-      <c r="AB7" s="10"/>
-      <c r="AC7" s="10"/>
-      <c r="AD7" s="10"/>
-      <c r="AE7" s="10"/>
-      <c r="AF7" s="10"/>
-      <c r="AG7" s="10"/>
-      <c r="AH7" s="10"/>
-      <c r="AI7" s="10"/>
+      <c r="Y7" s="32"/>
+      <c r="Z7" s="32"/>
+      <c r="AA7" s="32"/>
+      <c r="AB7" s="32"/>
+      <c r="AC7" s="32"/>
+      <c r="AD7" s="32"/>
+      <c r="AE7" s="32"/>
+      <c r="AF7" s="32"/>
+      <c r="AG7" s="32"/>
+      <c r="AH7" s="32"/>
+      <c r="AI7" s="32"/>
     </row>
     <row r="8" spans="1:37" ht="94.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="e" vm="2">
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="9" t="s">
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="Y8" s="10"/>
-      <c r="Z8" s="10"/>
-      <c r="AA8" s="10"/>
-      <c r="AB8" s="10"/>
-      <c r="AC8" s="10"/>
-      <c r="AD8" s="10"/>
-      <c r="AE8" s="10"/>
-      <c r="AF8" s="10"/>
-      <c r="AG8" s="10"/>
-      <c r="AH8" s="10"/>
-      <c r="AI8" s="10"/>
+      <c r="Y8" s="32"/>
+      <c r="Z8" s="32"/>
+      <c r="AA8" s="32"/>
+      <c r="AB8" s="32"/>
+      <c r="AC8" s="32"/>
+      <c r="AD8" s="32"/>
+      <c r="AE8" s="32"/>
+      <c r="AF8" s="32"/>
+      <c r="AG8" s="32"/>
+      <c r="AH8" s="32"/>
+      <c r="AI8" s="32"/>
     </row>
     <row r="9" spans="1:37" ht="129.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="e" vm="2">
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="9" t="s">
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="38"/>
+      <c r="X9" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="Y9" s="10"/>
-      <c r="Z9" s="10"/>
-      <c r="AA9" s="10"/>
-      <c r="AB9" s="10"/>
-      <c r="AC9" s="10"/>
-      <c r="AD9" s="10"/>
-      <c r="AE9" s="10"/>
-      <c r="AF9" s="10"/>
-      <c r="AG9" s="10"/>
-      <c r="AH9" s="10"/>
-      <c r="AI9" s="10"/>
+      <c r="Y9" s="32"/>
+      <c r="Z9" s="32"/>
+      <c r="AA9" s="32"/>
+      <c r="AB9" s="32"/>
+      <c r="AC9" s="32"/>
+      <c r="AD9" s="32"/>
+      <c r="AE9" s="32"/>
+      <c r="AF9" s="32"/>
+      <c r="AG9" s="32"/>
+      <c r="AH9" s="32"/>
+      <c r="AI9" s="32"/>
     </row>
     <row r="10" spans="1:37" ht="126" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="3" t="e" vm="2">
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="42" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="9" t="s">
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="44"/>
+      <c r="X10" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="Y10" s="10"/>
-      <c r="Z10" s="10"/>
-      <c r="AA10" s="10"/>
-      <c r="AB10" s="10"/>
-      <c r="AC10" s="10"/>
-      <c r="AD10" s="10"/>
-      <c r="AE10" s="10"/>
-      <c r="AF10" s="10"/>
-      <c r="AG10" s="10"/>
-      <c r="AH10" s="10"/>
-      <c r="AI10" s="10"/>
+      <c r="Y10" s="32"/>
+      <c r="Z10" s="32"/>
+      <c r="AA10" s="32"/>
+      <c r="AB10" s="32"/>
+      <c r="AC10" s="32"/>
+      <c r="AD10" s="32"/>
+      <c r="AE10" s="32"/>
+      <c r="AF10" s="32"/>
+      <c r="AG10" s="32"/>
+      <c r="AH10" s="32"/>
+      <c r="AI10" s="32"/>
     </row>
     <row r="11" spans="1:37" ht="165.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="e" vm="2">
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="9" t="s">
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="10"/>
-      <c r="AA11" s="10"/>
-      <c r="AB11" s="10"/>
-      <c r="AC11" s="10"/>
-      <c r="AD11" s="10"/>
-      <c r="AE11" s="10"/>
-      <c r="AF11" s="10"/>
-      <c r="AG11" s="10"/>
-      <c r="AH11" s="10"/>
-      <c r="AI11" s="10"/>
+      <c r="Y11" s="32"/>
+      <c r="Z11" s="32"/>
+      <c r="AA11" s="32"/>
+      <c r="AB11" s="32"/>
+      <c r="AC11" s="32"/>
+      <c r="AD11" s="32"/>
+      <c r="AE11" s="32"/>
+      <c r="AF11" s="32"/>
+      <c r="AG11" s="32"/>
+      <c r="AH11" s="32"/>
+      <c r="AI11" s="32"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="s">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10"/>
-      <c r="AB12" s="10"/>
-      <c r="AC12" s="10"/>
-      <c r="AD12" s="10"/>
-      <c r="AE12" s="10"/>
-      <c r="AF12" s="10"/>
-      <c r="AG12" s="10"/>
-      <c r="AH12" s="10"/>
-      <c r="AI12" s="10"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="32"/>
+      <c r="Z12" s="32"/>
+      <c r="AA12" s="32"/>
+      <c r="AB12" s="32"/>
+      <c r="AC12" s="32"/>
+      <c r="AD12" s="32"/>
+      <c r="AE12" s="32"/>
+      <c r="AF12" s="32"/>
+      <c r="AG12" s="32"/>
+      <c r="AH12" s="32"/>
+      <c r="AI12" s="32"/>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
-      <c r="AA13" s="10"/>
-      <c r="AB13" s="10"/>
-      <c r="AC13" s="10"/>
-      <c r="AD13" s="10"/>
-      <c r="AE13" s="10"/>
-      <c r="AF13" s="10"/>
-      <c r="AG13" s="10"/>
-      <c r="AH13" s="10"/>
-      <c r="AI13" s="10"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="38"/>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="38"/>
+      <c r="S13" s="38"/>
+      <c r="T13" s="38"/>
+      <c r="U13" s="38"/>
+      <c r="V13" s="38"/>
+      <c r="W13" s="38"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="32"/>
+      <c r="Z13" s="32"/>
+      <c r="AA13" s="32"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="32"/>
+      <c r="AD13" s="32"/>
+      <c r="AE13" s="32"/>
+      <c r="AF13" s="32"/>
+      <c r="AG13" s="32"/>
+      <c r="AH13" s="32"/>
+      <c r="AI13" s="32"/>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="10"/>
-      <c r="Z14" s="10"/>
-      <c r="AA14" s="10"/>
-      <c r="AB14" s="10"/>
-      <c r="AC14" s="10"/>
-      <c r="AD14" s="10"/>
-      <c r="AE14" s="10"/>
-      <c r="AF14" s="10"/>
-      <c r="AG14" s="10"/>
-      <c r="AH14" s="10"/>
-      <c r="AI14" s="10"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="38"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="38"/>
+      <c r="V14" s="38"/>
+      <c r="W14" s="38"/>
+      <c r="X14" s="31"/>
+      <c r="Y14" s="32"/>
+      <c r="Z14" s="32"/>
+      <c r="AA14" s="32"/>
+      <c r="AB14" s="32"/>
+      <c r="AC14" s="32"/>
+      <c r="AD14" s="32"/>
+      <c r="AE14" s="32"/>
+      <c r="AF14" s="32"/>
+      <c r="AG14" s="32"/>
+      <c r="AH14" s="32"/>
+      <c r="AI14" s="32"/>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="10"/>
-      <c r="AA15" s="10"/>
-      <c r="AB15" s="10"/>
-      <c r="AC15" s="10"/>
-      <c r="AD15" s="10"/>
-      <c r="AE15" s="10"/>
-      <c r="AF15" s="10"/>
-      <c r="AG15" s="10"/>
-      <c r="AH15" s="10"/>
-      <c r="AI15" s="10"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="38"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="38"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="32"/>
+      <c r="Z15" s="32"/>
+      <c r="AA15" s="32"/>
+      <c r="AB15" s="32"/>
+      <c r="AC15" s="32"/>
+      <c r="AD15" s="32"/>
+      <c r="AE15" s="32"/>
+      <c r="AF15" s="32"/>
+      <c r="AG15" s="32"/>
+      <c r="AH15" s="32"/>
+      <c r="AI15" s="32"/>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="10"/>
-      <c r="Z16" s="10"/>
-      <c r="AA16" s="10"/>
-      <c r="AB16" s="10"/>
-      <c r="AC16" s="10"/>
-      <c r="AD16" s="10"/>
-      <c r="AE16" s="10"/>
-      <c r="AF16" s="10"/>
-      <c r="AG16" s="10"/>
-      <c r="AH16" s="10"/>
-      <c r="AI16" s="10"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="38"/>
+      <c r="W16" s="38"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="32"/>
+      <c r="Z16" s="32"/>
+      <c r="AA16" s="32"/>
+      <c r="AB16" s="32"/>
+      <c r="AC16" s="32"/>
+      <c r="AD16" s="32"/>
+      <c r="AE16" s="32"/>
+      <c r="AF16" s="32"/>
+      <c r="AG16" s="32"/>
+      <c r="AH16" s="32"/>
+      <c r="AI16" s="32"/>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="10"/>
-      <c r="Z17" s="10"/>
-      <c r="AA17" s="10"/>
-      <c r="AB17" s="10"/>
-      <c r="AC17" s="10"/>
-      <c r="AD17" s="10"/>
-      <c r="AE17" s="10"/>
-      <c r="AF17" s="10"/>
-      <c r="AG17" s="10"/>
-      <c r="AH17" s="10"/>
-      <c r="AI17" s="10"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="38"/>
+      <c r="T17" s="38"/>
+      <c r="U17" s="38"/>
+      <c r="V17" s="38"/>
+      <c r="W17" s="38"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+      <c r="Z17" s="32"/>
+      <c r="AA17" s="32"/>
+      <c r="AB17" s="32"/>
+      <c r="AC17" s="32"/>
+      <c r="AD17" s="32"/>
+      <c r="AE17" s="32"/>
+      <c r="AF17" s="32"/>
+      <c r="AG17" s="32"/>
+      <c r="AH17" s="32"/>
+      <c r="AI17" s="32"/>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="10"/>
-      <c r="Z18" s="10"/>
-      <c r="AA18" s="10"/>
-      <c r="AB18" s="10"/>
-      <c r="AC18" s="10"/>
-      <c r="AD18" s="10"/>
-      <c r="AE18" s="10"/>
-      <c r="AF18" s="10"/>
-      <c r="AG18" s="10"/>
-      <c r="AH18" s="10"/>
-      <c r="AI18" s="10"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="38"/>
+      <c r="T18" s="38"/>
+      <c r="U18" s="38"/>
+      <c r="V18" s="38"/>
+      <c r="W18" s="38"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="32"/>
+      <c r="Z18" s="32"/>
+      <c r="AA18" s="32"/>
+      <c r="AB18" s="32"/>
+      <c r="AC18" s="32"/>
+      <c r="AD18" s="32"/>
+      <c r="AE18" s="32"/>
+      <c r="AF18" s="32"/>
+      <c r="AG18" s="32"/>
+      <c r="AH18" s="32"/>
+      <c r="AI18" s="32"/>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="10"/>
-      <c r="Z19" s="10"/>
-      <c r="AA19" s="10"/>
-      <c r="AB19" s="10"/>
-      <c r="AC19" s="10"/>
-      <c r="AD19" s="10"/>
-      <c r="AE19" s="10"/>
-      <c r="AF19" s="10"/>
-      <c r="AG19" s="10"/>
-      <c r="AH19" s="10"/>
-      <c r="AI19" s="10"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="38"/>
+      <c r="V19" s="38"/>
+      <c r="W19" s="38"/>
+      <c r="X19" s="31"/>
+      <c r="Y19" s="32"/>
+      <c r="Z19" s="32"/>
+      <c r="AA19" s="32"/>
+      <c r="AB19" s="32"/>
+      <c r="AC19" s="32"/>
+      <c r="AD19" s="32"/>
+      <c r="AE19" s="32"/>
+      <c r="AF19" s="32"/>
+      <c r="AG19" s="32"/>
+      <c r="AH19" s="32"/>
+      <c r="AI19" s="32"/>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="10"/>
-      <c r="Z20" s="10"/>
-      <c r="AA20" s="10"/>
-      <c r="AB20" s="10"/>
-      <c r="AC20" s="10"/>
-      <c r="AD20" s="10"/>
-      <c r="AE20" s="10"/>
-      <c r="AF20" s="10"/>
-      <c r="AG20" s="10"/>
-      <c r="AH20" s="10"/>
-      <c r="AI20" s="10"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38"/>
+      <c r="W20" s="38"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
+      <c r="AE20" s="32"/>
+      <c r="AF20" s="32"/>
+      <c r="AG20" s="32"/>
+      <c r="AH20" s="32"/>
+      <c r="AI20" s="32"/>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="10"/>
-      <c r="Z21" s="10"/>
-      <c r="AA21" s="10"/>
-      <c r="AB21" s="10"/>
-      <c r="AC21" s="10"/>
-      <c r="AD21" s="10"/>
-      <c r="AE21" s="10"/>
-      <c r="AF21" s="10"/>
-      <c r="AG21" s="10"/>
-      <c r="AH21" s="10"/>
-      <c r="AI21" s="10"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="38"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="38"/>
+      <c r="V21" s="38"/>
+      <c r="W21" s="38"/>
+      <c r="X21" s="31"/>
+      <c r="Y21" s="32"/>
+      <c r="Z21" s="32"/>
+      <c r="AA21" s="32"/>
+      <c r="AB21" s="32"/>
+      <c r="AC21" s="32"/>
+      <c r="AD21" s="32"/>
+      <c r="AE21" s="32"/>
+      <c r="AF21" s="32"/>
+      <c r="AG21" s="32"/>
+      <c r="AH21" s="32"/>
+      <c r="AI21" s="32"/>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="10"/>
-      <c r="Z22" s="10"/>
-      <c r="AA22" s="10"/>
-      <c r="AB22" s="10"/>
-      <c r="AC22" s="10"/>
-      <c r="AD22" s="10"/>
-      <c r="AE22" s="10"/>
-      <c r="AF22" s="10"/>
-      <c r="AG22" s="10"/>
-      <c r="AH22" s="10"/>
-      <c r="AI22" s="10"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="38"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="38"/>
+      <c r="T22" s="38"/>
+      <c r="U22" s="38"/>
+      <c r="V22" s="38"/>
+      <c r="W22" s="38"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="32"/>
+      <c r="Z22" s="32"/>
+      <c r="AA22" s="32"/>
+      <c r="AB22" s="32"/>
+      <c r="AC22" s="32"/>
+      <c r="AD22" s="32"/>
+      <c r="AE22" s="32"/>
+      <c r="AF22" s="32"/>
+      <c r="AG22" s="32"/>
+      <c r="AH22" s="32"/>
+      <c r="AI22" s="32"/>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="10"/>
-      <c r="Z23" s="10"/>
-      <c r="AA23" s="10"/>
-      <c r="AB23" s="10"/>
-      <c r="AC23" s="10"/>
-      <c r="AD23" s="10"/>
-      <c r="AE23" s="10"/>
-      <c r="AF23" s="10"/>
-      <c r="AG23" s="10"/>
-      <c r="AH23" s="10"/>
-      <c r="AI23" s="10"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="38"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="38"/>
+      <c r="V23" s="38"/>
+      <c r="W23" s="38"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="32"/>
+      <c r="Z23" s="32"/>
+      <c r="AA23" s="32"/>
+      <c r="AB23" s="32"/>
+      <c r="AC23" s="32"/>
+      <c r="AD23" s="32"/>
+      <c r="AE23" s="32"/>
+      <c r="AF23" s="32"/>
+      <c r="AG23" s="32"/>
+      <c r="AH23" s="32"/>
+      <c r="AI23" s="32"/>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="10"/>
-      <c r="Z24" s="10"/>
-      <c r="AA24" s="10"/>
-      <c r="AB24" s="10"/>
-      <c r="AC24" s="10"/>
-      <c r="AD24" s="10"/>
-      <c r="AE24" s="10"/>
-      <c r="AF24" s="10"/>
-      <c r="AG24" s="10"/>
-      <c r="AH24" s="10"/>
-      <c r="AI24" s="10"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="38"/>
+      <c r="T24" s="38"/>
+      <c r="U24" s="38"/>
+      <c r="V24" s="38"/>
+      <c r="W24" s="38"/>
+      <c r="X24" s="31"/>
+      <c r="Y24" s="32"/>
+      <c r="Z24" s="32"/>
+      <c r="AA24" s="32"/>
+      <c r="AB24" s="32"/>
+      <c r="AC24" s="32"/>
+      <c r="AD24" s="32"/>
+      <c r="AE24" s="32"/>
+      <c r="AF24" s="32"/>
+      <c r="AG24" s="32"/>
+      <c r="AH24" s="32"/>
+      <c r="AI24" s="32"/>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="10"/>
-      <c r="Z25" s="10"/>
-      <c r="AA25" s="10"/>
-      <c r="AB25" s="10"/>
-      <c r="AC25" s="10"/>
-      <c r="AD25" s="10"/>
-      <c r="AE25" s="10"/>
-      <c r="AF25" s="10"/>
-      <c r="AG25" s="10"/>
-      <c r="AH25" s="10"/>
-      <c r="AI25" s="10"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
+      <c r="P25" s="38"/>
+      <c r="Q25" s="38"/>
+      <c r="R25" s="38"/>
+      <c r="S25" s="38"/>
+      <c r="T25" s="38"/>
+      <c r="U25" s="38"/>
+      <c r="V25" s="38"/>
+      <c r="W25" s="38"/>
+      <c r="X25" s="31"/>
+      <c r="Y25" s="32"/>
+      <c r="Z25" s="32"/>
+      <c r="AA25" s="32"/>
+      <c r="AB25" s="32"/>
+      <c r="AC25" s="32"/>
+      <c r="AD25" s="32"/>
+      <c r="AE25" s="32"/>
+      <c r="AF25" s="32"/>
+      <c r="AG25" s="32"/>
+      <c r="AH25" s="32"/>
+      <c r="AI25" s="32"/>
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="10"/>
-      <c r="Z26" s="10"/>
-      <c r="AA26" s="10"/>
-      <c r="AB26" s="10"/>
-      <c r="AC26" s="10"/>
-      <c r="AD26" s="10"/>
-      <c r="AE26" s="10"/>
-      <c r="AF26" s="10"/>
-      <c r="AG26" s="10"/>
-      <c r="AH26" s="10"/>
-      <c r="AI26" s="10"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="38"/>
+      <c r="T26" s="38"/>
+      <c r="U26" s="38"/>
+      <c r="V26" s="38"/>
+      <c r="W26" s="38"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="32"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="32"/>
+      <c r="AF26" s="32"/>
+      <c r="AG26" s="32"/>
+      <c r="AH26" s="32"/>
+      <c r="AI26" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="J25:W25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="J26:W26"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="J23:W23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="J24:W24"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="J21:W21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="J22:W22"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="J19:W19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="J20:W20"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="J17:W17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="J18:W18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="J15:W15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="J16:W16"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="J13:W13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="J14:W14"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="J11:W11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="J12:W12"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="J9:W9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="J10:W10"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="J7:W7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="J8:W8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="J5:W5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="J6:W6"/>
+    <mergeCell ref="X2:AI2"/>
+    <mergeCell ref="X3:AI3"/>
+    <mergeCell ref="X4:AI4"/>
+    <mergeCell ref="X5:AI5"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="J4:W4"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="J1:W1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="J2:W2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="J3:W3"/>
     <mergeCell ref="X15:AI15"/>
     <mergeCell ref="X6:AI6"/>
     <mergeCell ref="X7:AI7"/>
@@ -2998,88 +3152,6 @@
     <mergeCell ref="X12:AI12"/>
     <mergeCell ref="X13:AI13"/>
     <mergeCell ref="X14:AI14"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="J1:W1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="J2:W2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="J3:W3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="J5:W5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="J6:W6"/>
-    <mergeCell ref="X2:AI2"/>
-    <mergeCell ref="X3:AI3"/>
-    <mergeCell ref="X4:AI4"/>
-    <mergeCell ref="X5:AI5"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="J4:W4"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="J9:W9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="J10:W10"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="J7:W7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="J8:W8"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="J13:W13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="J14:W14"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="J11:W11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="J12:W12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="J17:W17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="J18:W18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="J15:W15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="J16:W16"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:I21"/>
-    <mergeCell ref="J21:W21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:I22"/>
-    <mergeCell ref="J22:W22"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="J19:W19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:I20"/>
-    <mergeCell ref="J20:W20"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="J25:W25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="J26:W26"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:I23"/>
-    <mergeCell ref="J23:W23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="D24:I24"/>
-    <mergeCell ref="J24:W24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Project_SomethingAwesome/Project/outputs/requirements/Signal_Forge_CTF_Tasks.xlsx
+++ b/Project_SomethingAwesome/Project/outputs/requirements/Signal_Forge_CTF_Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GithubRepositories\COMP6841\Project_SomethingAwesome\Project\outputs\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869396F2-FCE2-479A-9FC5-9113E43B3940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BA87C8-36D2-4CA7-A67D-59EF5A6E3FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="109">
   <si>
     <t>Context ID</t>
   </si>
@@ -425,16 +425,26 @@
   <si>
     <t>FLAG{RANDU AINT GROGU}</t>
   </si>
+  <si>
+    <t>FLAG {I AM SCRAMBLING TO FIX THIS}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -600,153 +610,156 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1474,93 +1487,95 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="53" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="46">
+    <row r="10" spans="1:10" s="39" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="32">
         <v>3</v>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="32">
         <v>3</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="47" t="s">
+      <c r="D10" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="48" t="s">
+      <c r="E10" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="49" t="s">
+      <c r="F10" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="50" t="s">
+      <c r="G10" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="51"/>
-      <c r="I10" s="52" t="s">
+      <c r="H10" s="37"/>
+      <c r="I10" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="48" t="s">
+      <c r="J10" s="34" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="53" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="46">
+    <row r="11" spans="1:10" s="39" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="32">
         <v>3</v>
       </c>
-      <c r="B11" s="46">
+      <c r="B11" s="32">
         <v>3.01</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="48" t="s">
+      <c r="E11" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="50" t="s">
+      <c r="G11" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="51"/>
-      <c r="I11" s="52" t="s">
+      <c r="H11" s="37"/>
+      <c r="I11" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="48" t="s">
+      <c r="J11" s="62" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="61" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="54">
+    <row r="12" spans="1:10" s="46" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="40">
         <v>3</v>
       </c>
-      <c r="B12" s="54">
+      <c r="B12" s="40">
         <v>3.02</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="57" t="s">
+      <c r="F12" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="58" t="s">
+      <c r="G12" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="59"/>
-      <c r="I12" s="60" t="s">
+      <c r="H12" s="44"/>
+      <c r="I12" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="60"/>
+      <c r="J12" s="61" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="13" spans="1:10" s="16" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
@@ -1575,7 +1590,7 @@
       <c r="D13" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="45" t="s">
+      <c r="E13" s="31" t="s">
         <v>42</v>
       </c>
       <c r="F13" s="14" t="s">
@@ -1603,7 +1618,7 @@
       <c r="D14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="45" t="s">
+      <c r="E14" s="31" t="s">
         <v>44</v>
       </c>
       <c r="F14" s="14" t="s">
@@ -1991,1145 +2006,1063 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="33" t="s">
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="34"/>
-      <c r="AF1" s="34"/>
-      <c r="AG1" s="34"/>
-      <c r="AH1" s="34"/>
-      <c r="AI1" s="35"/>
+      <c r="Y1" s="59"/>
+      <c r="Z1" s="59"/>
+      <c r="AA1" s="59"/>
+      <c r="AB1" s="59"/>
+      <c r="AC1" s="59"/>
+      <c r="AD1" s="59"/>
+      <c r="AE1" s="59"/>
+      <c r="AF1" s="59"/>
+      <c r="AG1" s="59"/>
+      <c r="AH1" s="59"/>
+      <c r="AI1" s="60"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
     <row r="2" spans="1:37" ht="256.64999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="38" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39" t="e" vm="1">
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="40" t="s">
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="41"/>
-      <c r="AC2" s="41"/>
-      <c r="AD2" s="41"/>
-      <c r="AE2" s="41"/>
-      <c r="AF2" s="41"/>
-      <c r="AG2" s="41"/>
-      <c r="AH2" s="41"/>
-      <c r="AI2" s="41"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="53"/>
+      <c r="AB2" s="53"/>
+      <c r="AC2" s="53"/>
+      <c r="AD2" s="53"/>
+      <c r="AE2" s="53"/>
+      <c r="AF2" s="53"/>
+      <c r="AG2" s="53"/>
+      <c r="AH2" s="53"/>
+      <c r="AI2" s="53"/>
     </row>
     <row r="3" spans="1:37" ht="135.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="38" t="s">
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="38" t="e" vm="2">
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="47" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="31" t="s">
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
+      <c r="V3" s="51"/>
+      <c r="W3" s="51"/>
+      <c r="X3" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="Y3" s="32"/>
-      <c r="Z3" s="32"/>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="32"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="32"/>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
+      <c r="Y3" s="55"/>
+      <c r="Z3" s="55"/>
+      <c r="AA3" s="55"/>
+      <c r="AB3" s="55"/>
+      <c r="AC3" s="55"/>
+      <c r="AD3" s="55"/>
+      <c r="AE3" s="55"/>
+      <c r="AF3" s="55"/>
+      <c r="AG3" s="55"/>
+      <c r="AH3" s="55"/>
+      <c r="AI3" s="55"/>
     </row>
     <row r="4" spans="1:37" ht="169.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="38" t="s">
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38" t="e" vm="2">
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="39"/>
-      <c r="T4" s="39"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="39"/>
-      <c r="W4" s="39"/>
-      <c r="X4" s="31" t="s">
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="51"/>
+      <c r="W4" s="51"/>
+      <c r="X4" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="Y4" s="32"/>
-      <c r="Z4" s="32"/>
-      <c r="AA4" s="32"/>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="32"/>
-      <c r="AD4" s="32"/>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="32"/>
-      <c r="AG4" s="32"/>
-      <c r="AH4" s="32"/>
-      <c r="AI4" s="32"/>
+      <c r="Y4" s="55"/>
+      <c r="Z4" s="55"/>
+      <c r="AA4" s="55"/>
+      <c r="AB4" s="55"/>
+      <c r="AC4" s="55"/>
+      <c r="AD4" s="55"/>
+      <c r="AE4" s="55"/>
+      <c r="AF4" s="55"/>
+      <c r="AG4" s="55"/>
+      <c r="AH4" s="55"/>
+      <c r="AI4" s="55"/>
     </row>
     <row r="5" spans="1:37" ht="193" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="38" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39" t="e" vm="2">
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="39"/>
-      <c r="S5" s="39"/>
-      <c r="T5" s="39"/>
-      <c r="U5" s="39"/>
-      <c r="V5" s="39"/>
-      <c r="W5" s="39"/>
-      <c r="X5" s="31" t="s">
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="51"/>
+      <c r="P5" s="51"/>
+      <c r="Q5" s="51"/>
+      <c r="R5" s="51"/>
+      <c r="S5" s="51"/>
+      <c r="T5" s="51"/>
+      <c r="U5" s="51"/>
+      <c r="V5" s="51"/>
+      <c r="W5" s="51"/>
+      <c r="X5" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="Y5" s="32"/>
-      <c r="Z5" s="32"/>
-      <c r="AA5" s="32"/>
-      <c r="AB5" s="32"/>
-      <c r="AC5" s="32"/>
-      <c r="AD5" s="32"/>
-      <c r="AE5" s="32"/>
-      <c r="AF5" s="32"/>
-      <c r="AG5" s="32"/>
-      <c r="AH5" s="32"/>
-      <c r="AI5" s="32"/>
+      <c r="Y5" s="55"/>
+      <c r="Z5" s="55"/>
+      <c r="AA5" s="55"/>
+      <c r="AB5" s="55"/>
+      <c r="AC5" s="55"/>
+      <c r="AD5" s="55"/>
+      <c r="AE5" s="55"/>
+      <c r="AF5" s="55"/>
+      <c r="AG5" s="55"/>
+      <c r="AH5" s="55"/>
+      <c r="AI5" s="55"/>
     </row>
     <row r="6" spans="1:37" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="38" t="s">
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39" t="e" vm="2">
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="39"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="39"/>
-      <c r="W6" s="39"/>
-      <c r="X6" s="31" t="s">
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="51"/>
+      <c r="Q6" s="51"/>
+      <c r="R6" s="51"/>
+      <c r="S6" s="51"/>
+      <c r="T6" s="51"/>
+      <c r="U6" s="51"/>
+      <c r="V6" s="51"/>
+      <c r="W6" s="51"/>
+      <c r="X6" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="32"/>
-      <c r="AA6" s="32"/>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="32"/>
-      <c r="AD6" s="32"/>
-      <c r="AE6" s="32"/>
-      <c r="AF6" s="32"/>
-      <c r="AG6" s="32"/>
-      <c r="AH6" s="32"/>
-      <c r="AI6" s="32"/>
+      <c r="Y6" s="55"/>
+      <c r="Z6" s="55"/>
+      <c r="AA6" s="55"/>
+      <c r="AB6" s="55"/>
+      <c r="AC6" s="55"/>
+      <c r="AD6" s="55"/>
+      <c r="AE6" s="55"/>
+      <c r="AF6" s="55"/>
+      <c r="AG6" s="55"/>
+      <c r="AH6" s="55"/>
+      <c r="AI6" s="55"/>
     </row>
     <row r="7" spans="1:37" ht="106" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38" t="s">
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38" t="e" vm="2">
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="31" t="s">
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="47"/>
+      <c r="V7" s="47"/>
+      <c r="W7" s="47"/>
+      <c r="X7" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="Y7" s="32"/>
-      <c r="Z7" s="32"/>
-      <c r="AA7" s="32"/>
-      <c r="AB7" s="32"/>
-      <c r="AC7" s="32"/>
-      <c r="AD7" s="32"/>
-      <c r="AE7" s="32"/>
-      <c r="AF7" s="32"/>
-      <c r="AG7" s="32"/>
-      <c r="AH7" s="32"/>
-      <c r="AI7" s="32"/>
+      <c r="Y7" s="55"/>
+      <c r="Z7" s="55"/>
+      <c r="AA7" s="55"/>
+      <c r="AB7" s="55"/>
+      <c r="AC7" s="55"/>
+      <c r="AD7" s="55"/>
+      <c r="AE7" s="55"/>
+      <c r="AF7" s="55"/>
+      <c r="AG7" s="55"/>
+      <c r="AH7" s="55"/>
+      <c r="AI7" s="55"/>
     </row>
     <row r="8" spans="1:37" ht="94.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38" t="s">
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38" t="e" vm="2">
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="31" t="s">
+      <c r="K8" s="47"/>
+      <c r="L8" s="47"/>
+      <c r="M8" s="47"/>
+      <c r="N8" s="47"/>
+      <c r="O8" s="47"/>
+      <c r="P8" s="47"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="47"/>
+      <c r="U8" s="47"/>
+      <c r="V8" s="47"/>
+      <c r="W8" s="47"/>
+      <c r="X8" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="Y8" s="32"/>
-      <c r="Z8" s="32"/>
-      <c r="AA8" s="32"/>
-      <c r="AB8" s="32"/>
-      <c r="AC8" s="32"/>
-      <c r="AD8" s="32"/>
-      <c r="AE8" s="32"/>
-      <c r="AF8" s="32"/>
-      <c r="AG8" s="32"/>
-      <c r="AH8" s="32"/>
-      <c r="AI8" s="32"/>
+      <c r="Y8" s="55"/>
+      <c r="Z8" s="55"/>
+      <c r="AA8" s="55"/>
+      <c r="AB8" s="55"/>
+      <c r="AC8" s="55"/>
+      <c r="AD8" s="55"/>
+      <c r="AE8" s="55"/>
+      <c r="AF8" s="55"/>
+      <c r="AG8" s="55"/>
+      <c r="AH8" s="55"/>
+      <c r="AI8" s="55"/>
     </row>
     <row r="9" spans="1:37" ht="129.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38" t="s">
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38" t="e" vm="2">
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="38"/>
-      <c r="S9" s="38"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="38"/>
-      <c r="W9" s="38"/>
-      <c r="X9" s="31" t="s">
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="47"/>
+      <c r="N9" s="47"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="47"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="47"/>
+      <c r="U9" s="47"/>
+      <c r="V9" s="47"/>
+      <c r="W9" s="47"/>
+      <c r="X9" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="32"/>
-      <c r="AA9" s="32"/>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="32"/>
-      <c r="AD9" s="32"/>
-      <c r="AE9" s="32"/>
-      <c r="AF9" s="32"/>
-      <c r="AG9" s="32"/>
-      <c r="AH9" s="32"/>
-      <c r="AI9" s="32"/>
+      <c r="Y9" s="55"/>
+      <c r="Z9" s="55"/>
+      <c r="AA9" s="55"/>
+      <c r="AB9" s="55"/>
+      <c r="AC9" s="55"/>
+      <c r="AD9" s="55"/>
+      <c r="AE9" s="55"/>
+      <c r="AF9" s="55"/>
+      <c r="AG9" s="55"/>
+      <c r="AH9" s="55"/>
+      <c r="AI9" s="55"/>
     </row>
     <row r="10" spans="1:37" ht="126" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38" t="s">
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="42" t="e" vm="2">
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="48" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K10" s="43"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="44"/>
-      <c r="X10" s="31" t="s">
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="49"/>
+      <c r="W10" s="50"/>
+      <c r="X10" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="Y10" s="32"/>
-      <c r="Z10" s="32"/>
-      <c r="AA10" s="32"/>
-      <c r="AB10" s="32"/>
-      <c r="AC10" s="32"/>
-      <c r="AD10" s="32"/>
-      <c r="AE10" s="32"/>
-      <c r="AF10" s="32"/>
-      <c r="AG10" s="32"/>
-      <c r="AH10" s="32"/>
-      <c r="AI10" s="32"/>
+      <c r="Y10" s="55"/>
+      <c r="Z10" s="55"/>
+      <c r="AA10" s="55"/>
+      <c r="AB10" s="55"/>
+      <c r="AC10" s="55"/>
+      <c r="AD10" s="55"/>
+      <c r="AE10" s="55"/>
+      <c r="AF10" s="55"/>
+      <c r="AG10" s="55"/>
+      <c r="AH10" s="55"/>
+      <c r="AI10" s="55"/>
     </row>
     <row r="11" spans="1:37" ht="165.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38" t="s">
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38" t="e" vm="2">
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="38"/>
-      <c r="S11" s="38"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="31" t="s">
+      <c r="K11" s="47"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="47"/>
+      <c r="N11" s="47"/>
+      <c r="O11" s="47"/>
+      <c r="P11" s="47"/>
+      <c r="Q11" s="47"/>
+      <c r="R11" s="47"/>
+      <c r="S11" s="47"/>
+      <c r="T11" s="47"/>
+      <c r="U11" s="47"/>
+      <c r="V11" s="47"/>
+      <c r="W11" s="47"/>
+      <c r="X11" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="Y11" s="32"/>
-      <c r="Z11" s="32"/>
-      <c r="AA11" s="32"/>
-      <c r="AB11" s="32"/>
-      <c r="AC11" s="32"/>
-      <c r="AD11" s="32"/>
-      <c r="AE11" s="32"/>
-      <c r="AF11" s="32"/>
-      <c r="AG11" s="32"/>
-      <c r="AH11" s="32"/>
-      <c r="AI11" s="32"/>
+      <c r="Y11" s="55"/>
+      <c r="Z11" s="55"/>
+      <c r="AA11" s="55"/>
+      <c r="AB11" s="55"/>
+      <c r="AC11" s="55"/>
+      <c r="AD11" s="55"/>
+      <c r="AE11" s="55"/>
+      <c r="AF11" s="55"/>
+      <c r="AG11" s="55"/>
+      <c r="AH11" s="55"/>
+      <c r="AI11" s="55"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38" t="s">
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="31"/>
-      <c r="Y12" s="32"/>
-      <c r="Z12" s="32"/>
-      <c r="AA12" s="32"/>
-      <c r="AB12" s="32"/>
-      <c r="AC12" s="32"/>
-      <c r="AD12" s="32"/>
-      <c r="AE12" s="32"/>
-      <c r="AF12" s="32"/>
-      <c r="AG12" s="32"/>
-      <c r="AH12" s="32"/>
-      <c r="AI12" s="32"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="47"/>
+      <c r="V12" s="47"/>
+      <c r="W12" s="47"/>
+      <c r="X12" s="54"/>
+      <c r="Y12" s="55"/>
+      <c r="Z12" s="55"/>
+      <c r="AA12" s="55"/>
+      <c r="AB12" s="55"/>
+      <c r="AC12" s="55"/>
+      <c r="AD12" s="55"/>
+      <c r="AE12" s="55"/>
+      <c r="AF12" s="55"/>
+      <c r="AG12" s="55"/>
+      <c r="AH12" s="55"/>
+      <c r="AI12" s="55"/>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A13" s="38"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="38"/>
-      <c r="S13" s="38"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="32"/>
-      <c r="AA13" s="32"/>
-      <c r="AB13" s="32"/>
-      <c r="AC13" s="32"/>
-      <c r="AD13" s="32"/>
-      <c r="AE13" s="32"/>
-      <c r="AF13" s="32"/>
-      <c r="AG13" s="32"/>
-      <c r="AH13" s="32"/>
-      <c r="AI13" s="32"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="47"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="47"/>
+      <c r="V13" s="47"/>
+      <c r="W13" s="47"/>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="55"/>
+      <c r="Z13" s="55"/>
+      <c r="AA13" s="55"/>
+      <c r="AB13" s="55"/>
+      <c r="AC13" s="55"/>
+      <c r="AD13" s="55"/>
+      <c r="AE13" s="55"/>
+      <c r="AF13" s="55"/>
+      <c r="AG13" s="55"/>
+      <c r="AH13" s="55"/>
+      <c r="AI13" s="55"/>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A14" s="38"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="38"/>
-      <c r="Q14" s="38"/>
-      <c r="R14" s="38"/>
-      <c r="S14" s="38"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="31"/>
-      <c r="Y14" s="32"/>
-      <c r="Z14" s="32"/>
-      <c r="AA14" s="32"/>
-      <c r="AB14" s="32"/>
-      <c r="AC14" s="32"/>
-      <c r="AD14" s="32"/>
-      <c r="AE14" s="32"/>
-      <c r="AF14" s="32"/>
-      <c r="AG14" s="32"/>
-      <c r="AH14" s="32"/>
-      <c r="AI14" s="32"/>
+      <c r="A14" s="47"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47"/>
+      <c r="S14" s="47"/>
+      <c r="T14" s="47"/>
+      <c r="U14" s="47"/>
+      <c r="V14" s="47"/>
+      <c r="W14" s="47"/>
+      <c r="X14" s="54"/>
+      <c r="Y14" s="55"/>
+      <c r="Z14" s="55"/>
+      <c r="AA14" s="55"/>
+      <c r="AB14" s="55"/>
+      <c r="AC14" s="55"/>
+      <c r="AD14" s="55"/>
+      <c r="AE14" s="55"/>
+      <c r="AF14" s="55"/>
+      <c r="AG14" s="55"/>
+      <c r="AH14" s="55"/>
+      <c r="AI14" s="55"/>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A15" s="38"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="38"/>
-      <c r="R15" s="38"/>
-      <c r="S15" s="38"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="38"/>
-      <c r="W15" s="38"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="32"/>
-      <c r="Z15" s="32"/>
-      <c r="AA15" s="32"/>
-      <c r="AB15" s="32"/>
-      <c r="AC15" s="32"/>
-      <c r="AD15" s="32"/>
-      <c r="AE15" s="32"/>
-      <c r="AF15" s="32"/>
-      <c r="AG15" s="32"/>
-      <c r="AH15" s="32"/>
-      <c r="AI15" s="32"/>
+      <c r="A15" s="47"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="47"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="47"/>
+      <c r="S15" s="47"/>
+      <c r="T15" s="47"/>
+      <c r="U15" s="47"/>
+      <c r="V15" s="47"/>
+      <c r="W15" s="47"/>
+      <c r="X15" s="54"/>
+      <c r="Y15" s="55"/>
+      <c r="Z15" s="55"/>
+      <c r="AA15" s="55"/>
+      <c r="AB15" s="55"/>
+      <c r="AC15" s="55"/>
+      <c r="AD15" s="55"/>
+      <c r="AE15" s="55"/>
+      <c r="AF15" s="55"/>
+      <c r="AG15" s="55"/>
+      <c r="AH15" s="55"/>
+      <c r="AI15" s="55"/>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="38"/>
-      <c r="R16" s="38"/>
-      <c r="S16" s="38"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="38"/>
-      <c r="W16" s="38"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="32"/>
-      <c r="AA16" s="32"/>
-      <c r="AB16" s="32"/>
-      <c r="AC16" s="32"/>
-      <c r="AD16" s="32"/>
-      <c r="AE16" s="32"/>
-      <c r="AF16" s="32"/>
-      <c r="AG16" s="32"/>
-      <c r="AH16" s="32"/>
-      <c r="AI16" s="32"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="47"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="47"/>
+      <c r="N16" s="47"/>
+      <c r="O16" s="47"/>
+      <c r="P16" s="47"/>
+      <c r="Q16" s="47"/>
+      <c r="R16" s="47"/>
+      <c r="S16" s="47"/>
+      <c r="T16" s="47"/>
+      <c r="U16" s="47"/>
+      <c r="V16" s="47"/>
+      <c r="W16" s="47"/>
+      <c r="X16" s="54"/>
+      <c r="Y16" s="55"/>
+      <c r="Z16" s="55"/>
+      <c r="AA16" s="55"/>
+      <c r="AB16" s="55"/>
+      <c r="AC16" s="55"/>
+      <c r="AD16" s="55"/>
+      <c r="AE16" s="55"/>
+      <c r="AF16" s="55"/>
+      <c r="AG16" s="55"/>
+      <c r="AH16" s="55"/>
+      <c r="AI16" s="55"/>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A17" s="38"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="38"/>
-      <c r="R17" s="38"/>
-      <c r="S17" s="38"/>
-      <c r="T17" s="38"/>
-      <c r="U17" s="38"/>
-      <c r="V17" s="38"/>
-      <c r="W17" s="38"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="32"/>
-      <c r="Z17" s="32"/>
-      <c r="AA17" s="32"/>
-      <c r="AB17" s="32"/>
-      <c r="AC17" s="32"/>
-      <c r="AD17" s="32"/>
-      <c r="AE17" s="32"/>
-      <c r="AF17" s="32"/>
-      <c r="AG17" s="32"/>
-      <c r="AH17" s="32"/>
-      <c r="AI17" s="32"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="47"/>
+      <c r="L17" s="47"/>
+      <c r="M17" s="47"/>
+      <c r="N17" s="47"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="47"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="47"/>
+      <c r="T17" s="47"/>
+      <c r="U17" s="47"/>
+      <c r="V17" s="47"/>
+      <c r="W17" s="47"/>
+      <c r="X17" s="54"/>
+      <c r="Y17" s="55"/>
+      <c r="Z17" s="55"/>
+      <c r="AA17" s="55"/>
+      <c r="AB17" s="55"/>
+      <c r="AC17" s="55"/>
+      <c r="AD17" s="55"/>
+      <c r="AE17" s="55"/>
+      <c r="AF17" s="55"/>
+      <c r="AG17" s="55"/>
+      <c r="AH17" s="55"/>
+      <c r="AI17" s="55"/>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A18" s="38"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="38"/>
-      <c r="Q18" s="38"/>
-      <c r="R18" s="38"/>
-      <c r="S18" s="38"/>
-      <c r="T18" s="38"/>
-      <c r="U18" s="38"/>
-      <c r="V18" s="38"/>
-      <c r="W18" s="38"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="32"/>
-      <c r="Z18" s="32"/>
-      <c r="AA18" s="32"/>
-      <c r="AB18" s="32"/>
-      <c r="AC18" s="32"/>
-      <c r="AD18" s="32"/>
-      <c r="AE18" s="32"/>
-      <c r="AF18" s="32"/>
-      <c r="AG18" s="32"/>
-      <c r="AH18" s="32"/>
-      <c r="AI18" s="32"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="47"/>
+      <c r="M18" s="47"/>
+      <c r="N18" s="47"/>
+      <c r="O18" s="47"/>
+      <c r="P18" s="47"/>
+      <c r="Q18" s="47"/>
+      <c r="R18" s="47"/>
+      <c r="S18" s="47"/>
+      <c r="T18" s="47"/>
+      <c r="U18" s="47"/>
+      <c r="V18" s="47"/>
+      <c r="W18" s="47"/>
+      <c r="X18" s="54"/>
+      <c r="Y18" s="55"/>
+      <c r="Z18" s="55"/>
+      <c r="AA18" s="55"/>
+      <c r="AB18" s="55"/>
+      <c r="AC18" s="55"/>
+      <c r="AD18" s="55"/>
+      <c r="AE18" s="55"/>
+      <c r="AF18" s="55"/>
+      <c r="AG18" s="55"/>
+      <c r="AH18" s="55"/>
+      <c r="AI18" s="55"/>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A19" s="38"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="38"/>
-      <c r="R19" s="38"/>
-      <c r="S19" s="38"/>
-      <c r="T19" s="38"/>
-      <c r="U19" s="38"/>
-      <c r="V19" s="38"/>
-      <c r="W19" s="38"/>
-      <c r="X19" s="31"/>
-      <c r="Y19" s="32"/>
-      <c r="Z19" s="32"/>
-      <c r="AA19" s="32"/>
-      <c r="AB19" s="32"/>
-      <c r="AC19" s="32"/>
-      <c r="AD19" s="32"/>
-      <c r="AE19" s="32"/>
-      <c r="AF19" s="32"/>
-      <c r="AG19" s="32"/>
-      <c r="AH19" s="32"/>
-      <c r="AI19" s="32"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="47"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="47"/>
+      <c r="V19" s="47"/>
+      <c r="W19" s="47"/>
+      <c r="X19" s="54"/>
+      <c r="Y19" s="55"/>
+      <c r="Z19" s="55"/>
+      <c r="AA19" s="55"/>
+      <c r="AB19" s="55"/>
+      <c r="AC19" s="55"/>
+      <c r="AD19" s="55"/>
+      <c r="AE19" s="55"/>
+      <c r="AF19" s="55"/>
+      <c r="AG19" s="55"/>
+      <c r="AH19" s="55"/>
+      <c r="AI19" s="55"/>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A20" s="38"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38"/>
-      <c r="R20" s="38"/>
-      <c r="S20" s="38"/>
-      <c r="T20" s="38"/>
-      <c r="U20" s="38"/>
-      <c r="V20" s="38"/>
-      <c r="W20" s="38"/>
-      <c r="X20" s="31"/>
-      <c r="Y20" s="32"/>
-      <c r="Z20" s="32"/>
-      <c r="AA20" s="32"/>
-      <c r="AB20" s="32"/>
-      <c r="AC20" s="32"/>
-      <c r="AD20" s="32"/>
-      <c r="AE20" s="32"/>
-      <c r="AF20" s="32"/>
-      <c r="AG20" s="32"/>
-      <c r="AH20" s="32"/>
-      <c r="AI20" s="32"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="47"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="47"/>
+      <c r="R20" s="47"/>
+      <c r="S20" s="47"/>
+      <c r="T20" s="47"/>
+      <c r="U20" s="47"/>
+      <c r="V20" s="47"/>
+      <c r="W20" s="47"/>
+      <c r="X20" s="54"/>
+      <c r="Y20" s="55"/>
+      <c r="Z20" s="55"/>
+      <c r="AA20" s="55"/>
+      <c r="AB20" s="55"/>
+      <c r="AC20" s="55"/>
+      <c r="AD20" s="55"/>
+      <c r="AE20" s="55"/>
+      <c r="AF20" s="55"/>
+      <c r="AG20" s="55"/>
+      <c r="AH20" s="55"/>
+      <c r="AI20" s="55"/>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A21" s="38"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="38"/>
-      <c r="T21" s="38"/>
-      <c r="U21" s="38"/>
-      <c r="V21" s="38"/>
-      <c r="W21" s="38"/>
-      <c r="X21" s="31"/>
-      <c r="Y21" s="32"/>
-      <c r="Z21" s="32"/>
-      <c r="AA21" s="32"/>
-      <c r="AB21" s="32"/>
-      <c r="AC21" s="32"/>
-      <c r="AD21" s="32"/>
-      <c r="AE21" s="32"/>
-      <c r="AF21" s="32"/>
-      <c r="AG21" s="32"/>
-      <c r="AH21" s="32"/>
-      <c r="AI21" s="32"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
+      <c r="N21" s="47"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="47"/>
+      <c r="Q21" s="47"/>
+      <c r="R21" s="47"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="47"/>
+      <c r="U21" s="47"/>
+      <c r="V21" s="47"/>
+      <c r="W21" s="47"/>
+      <c r="X21" s="54"/>
+      <c r="Y21" s="55"/>
+      <c r="Z21" s="55"/>
+      <c r="AA21" s="55"/>
+      <c r="AB21" s="55"/>
+      <c r="AC21" s="55"/>
+      <c r="AD21" s="55"/>
+      <c r="AE21" s="55"/>
+      <c r="AF21" s="55"/>
+      <c r="AG21" s="55"/>
+      <c r="AH21" s="55"/>
+      <c r="AI21" s="55"/>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A22" s="38"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="38"/>
-      <c r="R22" s="38"/>
-      <c r="S22" s="38"/>
-      <c r="T22" s="38"/>
-      <c r="U22" s="38"/>
-      <c r="V22" s="38"/>
-      <c r="W22" s="38"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="32"/>
-      <c r="Z22" s="32"/>
-      <c r="AA22" s="32"/>
-      <c r="AB22" s="32"/>
-      <c r="AC22" s="32"/>
-      <c r="AD22" s="32"/>
-      <c r="AE22" s="32"/>
-      <c r="AF22" s="32"/>
-      <c r="AG22" s="32"/>
-      <c r="AH22" s="32"/>
-      <c r="AI22" s="32"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="47"/>
+      <c r="M22" s="47"/>
+      <c r="N22" s="47"/>
+      <c r="O22" s="47"/>
+      <c r="P22" s="47"/>
+      <c r="Q22" s="47"/>
+      <c r="R22" s="47"/>
+      <c r="S22" s="47"/>
+      <c r="T22" s="47"/>
+      <c r="U22" s="47"/>
+      <c r="V22" s="47"/>
+      <c r="W22" s="47"/>
+      <c r="X22" s="54"/>
+      <c r="Y22" s="55"/>
+      <c r="Z22" s="55"/>
+      <c r="AA22" s="55"/>
+      <c r="AB22" s="55"/>
+      <c r="AC22" s="55"/>
+      <c r="AD22" s="55"/>
+      <c r="AE22" s="55"/>
+      <c r="AF22" s="55"/>
+      <c r="AG22" s="55"/>
+      <c r="AH22" s="55"/>
+      <c r="AI22" s="55"/>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A23" s="38"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-      <c r="R23" s="38"/>
-      <c r="S23" s="38"/>
-      <c r="T23" s="38"/>
-      <c r="U23" s="38"/>
-      <c r="V23" s="38"/>
-      <c r="W23" s="38"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="32"/>
-      <c r="Z23" s="32"/>
-      <c r="AA23" s="32"/>
-      <c r="AB23" s="32"/>
-      <c r="AC23" s="32"/>
-      <c r="AD23" s="32"/>
-      <c r="AE23" s="32"/>
-      <c r="AF23" s="32"/>
-      <c r="AG23" s="32"/>
-      <c r="AH23" s="32"/>
-      <c r="AI23" s="32"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="47"/>
+      <c r="N23" s="47"/>
+      <c r="O23" s="47"/>
+      <c r="P23" s="47"/>
+      <c r="Q23" s="47"/>
+      <c r="R23" s="47"/>
+      <c r="S23" s="47"/>
+      <c r="T23" s="47"/>
+      <c r="U23" s="47"/>
+      <c r="V23" s="47"/>
+      <c r="W23" s="47"/>
+      <c r="X23" s="54"/>
+      <c r="Y23" s="55"/>
+      <c r="Z23" s="55"/>
+      <c r="AA23" s="55"/>
+      <c r="AB23" s="55"/>
+      <c r="AC23" s="55"/>
+      <c r="AD23" s="55"/>
+      <c r="AE23" s="55"/>
+      <c r="AF23" s="55"/>
+      <c r="AG23" s="55"/>
+      <c r="AH23" s="55"/>
+      <c r="AI23" s="55"/>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A24" s="38"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="38"/>
-      <c r="Q24" s="38"/>
-      <c r="R24" s="38"/>
-      <c r="S24" s="38"/>
-      <c r="T24" s="38"/>
-      <c r="U24" s="38"/>
-      <c r="V24" s="38"/>
-      <c r="W24" s="38"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="32"/>
-      <c r="Z24" s="32"/>
-      <c r="AA24" s="32"/>
-      <c r="AB24" s="32"/>
-      <c r="AC24" s="32"/>
-      <c r="AD24" s="32"/>
-      <c r="AE24" s="32"/>
-      <c r="AF24" s="32"/>
-      <c r="AG24" s="32"/>
-      <c r="AH24" s="32"/>
-      <c r="AI24" s="32"/>
+      <c r="A24" s="47"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="47"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="47"/>
+      <c r="N24" s="47"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="47"/>
+      <c r="Q24" s="47"/>
+      <c r="R24" s="47"/>
+      <c r="S24" s="47"/>
+      <c r="T24" s="47"/>
+      <c r="U24" s="47"/>
+      <c r="V24" s="47"/>
+      <c r="W24" s="47"/>
+      <c r="X24" s="54"/>
+      <c r="Y24" s="55"/>
+      <c r="Z24" s="55"/>
+      <c r="AA24" s="55"/>
+      <c r="AB24" s="55"/>
+      <c r="AC24" s="55"/>
+      <c r="AD24" s="55"/>
+      <c r="AE24" s="55"/>
+      <c r="AF24" s="55"/>
+      <c r="AG24" s="55"/>
+      <c r="AH24" s="55"/>
+      <c r="AI24" s="55"/>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A25" s="38"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
-      <c r="R25" s="38"/>
-      <c r="S25" s="38"/>
-      <c r="T25" s="38"/>
-      <c r="U25" s="38"/>
-      <c r="V25" s="38"/>
-      <c r="W25" s="38"/>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="32"/>
-      <c r="Z25" s="32"/>
-      <c r="AA25" s="32"/>
-      <c r="AB25" s="32"/>
-      <c r="AC25" s="32"/>
-      <c r="AD25" s="32"/>
-      <c r="AE25" s="32"/>
-      <c r="AF25" s="32"/>
-      <c r="AG25" s="32"/>
-      <c r="AH25" s="32"/>
-      <c r="AI25" s="32"/>
+      <c r="A25" s="47"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
+      <c r="M25" s="47"/>
+      <c r="N25" s="47"/>
+      <c r="O25" s="47"/>
+      <c r="P25" s="47"/>
+      <c r="Q25" s="47"/>
+      <c r="R25" s="47"/>
+      <c r="S25" s="47"/>
+      <c r="T25" s="47"/>
+      <c r="U25" s="47"/>
+      <c r="V25" s="47"/>
+      <c r="W25" s="47"/>
+      <c r="X25" s="54"/>
+      <c r="Y25" s="55"/>
+      <c r="Z25" s="55"/>
+      <c r="AA25" s="55"/>
+      <c r="AB25" s="55"/>
+      <c r="AC25" s="55"/>
+      <c r="AD25" s="55"/>
+      <c r="AE25" s="55"/>
+      <c r="AF25" s="55"/>
+      <c r="AG25" s="55"/>
+      <c r="AH25" s="55"/>
+      <c r="AI25" s="55"/>
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A26" s="38"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="38"/>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
-      <c r="S26" s="38"/>
-      <c r="T26" s="38"/>
-      <c r="U26" s="38"/>
-      <c r="V26" s="38"/>
-      <c r="W26" s="38"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="32"/>
-      <c r="Z26" s="32"/>
-      <c r="AA26" s="32"/>
-      <c r="AB26" s="32"/>
-      <c r="AC26" s="32"/>
-      <c r="AD26" s="32"/>
-      <c r="AE26" s="32"/>
-      <c r="AF26" s="32"/>
-      <c r="AG26" s="32"/>
-      <c r="AH26" s="32"/>
-      <c r="AI26" s="32"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="47"/>
+      <c r="N26" s="47"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="47"/>
+      <c r="Q26" s="47"/>
+      <c r="R26" s="47"/>
+      <c r="S26" s="47"/>
+      <c r="T26" s="47"/>
+      <c r="U26" s="47"/>
+      <c r="V26" s="47"/>
+      <c r="W26" s="47"/>
+      <c r="X26" s="54"/>
+      <c r="Y26" s="55"/>
+      <c r="Z26" s="55"/>
+      <c r="AA26" s="55"/>
+      <c r="AB26" s="55"/>
+      <c r="AC26" s="55"/>
+      <c r="AD26" s="55"/>
+      <c r="AE26" s="55"/>
+      <c r="AF26" s="55"/>
+      <c r="AG26" s="55"/>
+      <c r="AH26" s="55"/>
+      <c r="AI26" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="J25:W25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="J26:W26"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:I23"/>
-    <mergeCell ref="J23:W23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="D24:I24"/>
-    <mergeCell ref="J24:W24"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:I21"/>
-    <mergeCell ref="J21:W21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:I22"/>
-    <mergeCell ref="J22:W22"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="J19:W19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:I20"/>
-    <mergeCell ref="J20:W20"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="J17:W17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="J18:W18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="J15:W15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="J16:W16"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="J13:W13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="J14:W14"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="J11:W11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="J12:W12"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="J9:W9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="J10:W10"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="J7:W7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="J8:W8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="J5:W5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="J6:W6"/>
-    <mergeCell ref="X2:AI2"/>
-    <mergeCell ref="X3:AI3"/>
-    <mergeCell ref="X4:AI4"/>
-    <mergeCell ref="X5:AI5"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="J4:W4"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="J1:W1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="J2:W2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="J3:W3"/>
     <mergeCell ref="X15:AI15"/>
     <mergeCell ref="X6:AI6"/>
     <mergeCell ref="X7:AI7"/>
@@ -3152,6 +3085,88 @@
     <mergeCell ref="X12:AI12"/>
     <mergeCell ref="X13:AI13"/>
     <mergeCell ref="X14:AI14"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="J1:W1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="J2:W2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="J3:W3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="J5:W5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="J6:W6"/>
+    <mergeCell ref="X2:AI2"/>
+    <mergeCell ref="X3:AI3"/>
+    <mergeCell ref="X4:AI4"/>
+    <mergeCell ref="X5:AI5"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="J4:W4"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="J9:W9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="J10:W10"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="J7:W7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="J8:W8"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="J13:W13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="J14:W14"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="J11:W11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="J12:W12"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="J17:W17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="J18:W18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="J15:W15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="J16:W16"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="J21:W21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="J22:W22"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="J19:W19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="J20:W20"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="J25:W25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="J26:W26"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="J23:W23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="J24:W24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
